--- a/314e-ig/output/StructureDefinition-datetime-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datetime-314e.xlsx
@@ -36,7 +36,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>DateTime314e</t>
+    <t>dateTime314e</t>
   </si>
   <si>
     <t>Title</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-16T16:45:26+05:30</t>
+    <t>2026-05-17T00:25:02+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -83,11 +83,11 @@
   <si>
     <t>314e profile of the FHIR dateTime primitive datatype.
 All dateTime values SHALL be stored in UTC.
-If only a smaller degree of precision is verifiable or usable
+If only a smaller degree of precision is usable
 (for example, only the date portion is known),
 the following extension SHALL be used:
 http://314e.com/fhir/StructureDefinition/datetime-precision-314e
-If the date/time value is approximate rather than exact,
+If all or part of the usable date/time value is approximate rather than exact,
 the following extension SHALL be used:
 https://hl7.org.au/fhir/StructureDefinition/date-accuracy-indicator</t>
   </si>
@@ -322,8 +322,8 @@
     <t>Usable precision of the dateTime value</t>
   </si>
   <si>
-    <t>Specifies the degree of precision that is usable,
-reliable, or verifiable for the dateTime value.
+    <t>Specifies the degree of precision that is meaningful, usable
+or reliable for the dateTime value.
 Example:
 - year
 - month
@@ -349,7 +349,7 @@
     <t>Indicates the precision that is verified as clinically exact or accurate</t>
   </si>
   <si>
-    <t>Specifies the accuracy or exactness of a dateTime value when only some portion of 
+    <t>Specifies the accuracy or exactness of a dateTime value when only some part of 
 the known/ usable precision of dateTime can be verified as accurate or exact and the rest is estimated or approximate. 
 Examples include year-only, month-level, date-level, full timestamp precision or none.</t>
   </si>

--- a/314e-ig/output/StructureDefinition-datetime-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datetime-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-17T00:25:02+05:30</t>
+    <t>2026-05-19T06:46:39+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-datetime-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datetime-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-19T06:46:39+05:30</t>
+    <t>2026-05-19T11:54:54+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-datetime-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datetime-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-19T11:54:54+05:30</t>
+    <t>2026-05-25T12:07:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-datetime-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datetime-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T12:07:44+05:30</t>
+    <t>2026-05-25T12:34:12+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-datetime-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datetime-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T12:34:12+05:30</t>
+    <t>2026-05-25T13:52:53+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-datetime-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datetime-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T13:52:53+05:30</t>
+    <t>2026-05-25T14:14:21+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-datetime-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datetime-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T14:14:21+05:30</t>
+    <t>2026-05-25T14:26:28+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-datetime-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datetime-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T14:26:28+05:30</t>
+    <t>2026-05-25T14:41:34+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-datetime-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datetime-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T14:41:34+05:30</t>
+    <t>2026-05-25T15:12:42+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-datetime-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datetime-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:12:42+05:30</t>
+    <t>2026-05-25T15:24:41+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-datetime-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datetime-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:24:41+05:30</t>
+    <t>2026-05-25T15:48:57+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-datetime-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datetime-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:48:57+05:30</t>
+    <t>2026-05-25T16:36:06+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-datetime-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datetime-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T16:36:06+05:30</t>
+    <t>2026-05-26T08:48:22+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-datetime-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datetime-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T08:48:22+05:30</t>
+    <t>2026-05-26T12:06:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-datetime-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datetime-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T12:06:33+05:30</t>
+    <t>2026-05-26T19:54:55+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-datetime-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datetime-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T19:54:55+05:30</t>
+    <t>2026-06-10T16:33:40+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -86,7 +86,7 @@
 If only a smaller degree of precision is usable
 (for example, only the date portion is known),
 the following extension SHALL be used:
-http://314e.com/fhir/StructureDefinition/datetime-precision-314e
+http://314e.com/fhir/StructureDefinition/datetime-precision
 If all or part of the usable date/time value is approximate rather than exact,
 the following extension SHALL be used:
 https://hl7.org.au/fhir/StructureDefinition/date-accuracy-indicator</t>
@@ -315,7 +315,7 @@
     <t>timePrecision</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://314e.com/fhir/StructureDefinition/datetime-precision-314e}
+    <t xml:space="preserve">Extension {http://314e.com/fhir/StructureDefinition/datetime-precision}
 </t>
   </si>
   <si>
@@ -342,7 +342,7 @@
     <t>accuracyIndicator</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://314e.com/fhir/StructureDefinition/datetime-accuracy-314e}
+    <t xml:space="preserve">Extension {http://314e.com/fhir/StructureDefinition/datetime-accuracy}
 </t>
   </si>
   <si>
@@ -679,7 +679,7 @@
     <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="64.0625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="59.4765625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/314e-ig/output/StructureDefinition-datetime-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datetime-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T16:33:40+05:30</t>
+    <t>2026-06-11T14:17:09+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-datetime-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datetime-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:17:09+05:30</t>
+    <t>2026-06-18T13:36:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-datetime-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datetime-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:36:33+05:30</t>
+    <t>2026-06-18T14:15:04+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-datetime-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datetime-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:15:04+05:30</t>
+    <t>2026-06-18T16:14:31+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-datetime-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datetime-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T16:14:31+05:30</t>
+    <t>2026-06-24T16:34:23+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-datetime-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datetime-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:34:23+05:30</t>
+    <t>2026-06-29T17:18:47+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-datetime-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datetime-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:18:47+05:30</t>
+    <t>2026-07-01T18:18:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
